--- a/new code and db logic/DB_schema.xlsx
+++ b/new code and db logic/DB_schema.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janarddanm\Downloads\01-07-2026\DIP-Parquet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\S2\Test\DST 2.0_2026\10.PFG_Final\new code and db logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E85C566-92EE-4479-8322-A535331AC36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D91998-B23F-4628-AD6A-49516BCDEAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5AB18C5-F8B5-439A-BA8C-D3B43E35A3B8}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A5AB18C5-F8B5-439A-BA8C-D3B43E35A3B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="182">
   <si>
     <t>ModuleName</t>
   </si>
@@ -474,6 +477,117 @@
   </si>
   <si>
     <t>53D9C70D-69D8-4F93-AF1A-55802E74FF96</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>COAID</t>
+  </si>
+  <si>
+    <t>AdditionalInfoId</t>
+  </si>
+  <si>
+    <t>AuditorsSignatureDate</t>
+  </si>
+  <si>
+    <t>EntityCity</t>
+  </si>
+  <si>
+    <t>EntityState</t>
+  </si>
+  <si>
+    <t>EntityContactName</t>
+  </si>
+  <si>
+    <t>EntityContactTitle</t>
+  </si>
+  <si>
+    <t>EntityContactPhone</t>
+  </si>
+  <si>
+    <t>EntityContactEmail</t>
+  </si>
+  <si>
+    <t>AuditorFirmName</t>
+  </si>
+  <si>
+    <t>AuditorName</t>
+  </si>
+  <si>
+    <t>AuditorContactPhone</t>
+  </si>
+  <si>
+    <t>AuditorContactEmail</t>
+  </si>
+  <si>
+    <t>Column_name</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Computed</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Prec</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>Nullable</t>
+  </si>
+  <si>
+    <t>TrimTrailingBlanks</t>
+  </si>
+  <si>
+    <t>FixedLenNullInSource</t>
+  </si>
+  <si>
+    <t>Collation</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>(n/a)</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>uniqueidentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t>bit</t>
+  </si>
+  <si>
+    <t>char</t>
+  </si>
+  <si>
+    <t>SQL_Latin1_General_CP1_CI_AS</t>
+  </si>
+  <si>
+    <t>varchar</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>datetime2</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
 </sst>
 </file>
@@ -607,12 +721,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -622,17 +744,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1003,44 +1114,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="7"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="13"/>
       <c r="M1" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="11" t="s">
+      <c r="C2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -1174,25 +1285,25 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -1260,7 +1371,7 @@
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+      <c r="A14" s="2">
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1276,29 +1387,29 @@
       <c r="H14" s="2"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="6" t="s">
         <v>27</v>
       </c>
       <c r="E19" s="4" t="s">
@@ -1375,37 +1486,37 @@
       <c r="I22" s="2"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
       <c r="X26" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="6" t="s">
         <v>65</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -1414,7 +1525,7 @@
       <c r="C27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E27" s="4" t="s">
@@ -1489,7 +1600,7 @@
       <c r="E28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="7" t="s">
         <v>56</v>
       </c>
       <c r="G28" s="2" t="s">
@@ -1558,7 +1669,7 @@
       <c r="E29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="7" t="s">
         <v>58</v>
       </c>
       <c r="G29" s="2" t="s">
@@ -1612,25 +1723,25 @@
       <c r="W29" s="2"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -1698,38 +1809,38 @@
       <c r="H37" s="2"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
       <c r="M40" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="6" t="s">
         <v>72</v>
       </c>
       <c r="F41" s="4" t="s">
@@ -1747,10 +1858,10 @@
       <c r="J41" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="K41" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="L41" s="6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1983,7 +2094,7 @@
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="10">
+      <c r="A48" s="2">
         <v>17</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -2027,25 +2138,25 @@
       <c r="H50" s="1"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D53" s="4" t="s">
@@ -2116,10 +2227,10 @@
       <c r="A57" s="2">
         <v>4</v>
       </c>
-      <c r="B57" s="10">
-        <v>1</v>
-      </c>
-      <c r="C57" s="10">
+      <c r="B57" s="2">
+        <v>1</v>
+      </c>
+      <c r="C57" s="2">
         <v>14</v>
       </c>
       <c r="D57" s="2"/>
@@ -2132,10 +2243,10 @@
       <c r="A58" s="2">
         <v>5</v>
       </c>
-      <c r="B58" s="10">
-        <v>1</v>
-      </c>
-      <c r="C58" s="10">
+      <c r="B58" s="2">
+        <v>1</v>
+      </c>
+      <c r="C58" s="2">
         <v>15</v>
       </c>
       <c r="D58" s="2"/>
@@ -2148,10 +2259,10 @@
       <c r="A59" s="2">
         <v>6</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="2">
         <v>2</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C59" s="2">
         <v>11</v>
       </c>
       <c r="D59" s="2"/>
@@ -2164,10 +2275,10 @@
       <c r="A60" s="2">
         <v>7</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="2">
         <v>2</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C60" s="2">
         <v>12</v>
       </c>
       <c r="D60" s="2"/>
@@ -2177,13 +2288,13 @@
       <c r="H60" s="2"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="10">
+      <c r="A61" s="2">
         <v>8</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="2">
         <v>2</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="2">
         <v>15</v>
       </c>
       <c r="D61" s="2"/>
@@ -2193,13 +2304,13 @@
       <c r="H61" s="2"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="10">
+      <c r="A62" s="2">
         <v>9</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="2">
         <v>3</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C62" s="2">
         <v>15</v>
       </c>
       <c r="D62" s="2"/>
@@ -2209,13 +2320,13 @@
       <c r="H62" s="2"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="10">
+      <c r="A63" s="2">
         <v>10</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="2">
         <v>3</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C63" s="2">
         <v>16</v>
       </c>
       <c r="D63" s="2"/>
@@ -2225,13 +2336,13 @@
       <c r="H63" s="2"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="9">
+      <c r="A64" s="5">
         <v>11</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="2">
         <v>3</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="2">
         <v>17</v>
       </c>
       <c r="D64" s="2"/>
@@ -2240,59 +2351,29 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-    </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-    </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-    </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
       <c r="I68" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="6" t="s">
         <v>127</v>
       </c>
       <c r="D69" s="4" t="s">
@@ -2393,60 +2474,60 @@
       <c r="E73" s="1"/>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
-      <c r="N76" s="8"/>
-      <c r="O76" s="8"/>
-      <c r="P76" s="8"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="8"/>
-      <c r="U76" s="8"/>
-      <c r="V76" s="8"/>
-      <c r="W76" s="8"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="8"/>
-      <c r="Z76" s="8"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="10"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="10"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
+      <c r="S76" s="10"/>
+      <c r="T76" s="10"/>
+      <c r="U76" s="10"/>
+      <c r="V76" s="10"/>
+      <c r="W76" s="10"/>
+      <c r="X76" s="10"/>
+      <c r="Y76" s="10"/>
+      <c r="Z76" s="10"/>
+      <c r="AA76" s="10"/>
+      <c r="AB76" s="10"/>
       <c r="AC76" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E77" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G77" s="11" t="s">
+      <c r="G77" s="6" t="s">
         <v>105</v>
       </c>
       <c r="H77" s="4" t="s">
@@ -2565,9 +2646,9 @@
       <c r="Q78" s="2"/>
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
-      <c r="T78" s="15"/>
-      <c r="U78" s="15"/>
-      <c r="V78" s="15"/>
+      <c r="T78" s="8"/>
+      <c r="U78" s="8"/>
+      <c r="V78" s="8"/>
       <c r="W78" s="2"/>
       <c r="X78" s="3"/>
       <c r="Y78" s="2"/>
@@ -2886,25 +2967,25 @@
       <c r="AB83" s="2"/>
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A84" s="16">
+      <c r="A84" s="9">
         <v>7</v>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="9">
         <v>107</v>
       </c>
-      <c r="C84" s="16">
-        <v>1</v>
-      </c>
-      <c r="D84" s="16">
+      <c r="C84" s="9">
+        <v>1</v>
+      </c>
+      <c r="D84" s="9">
         <v>15</v>
       </c>
-      <c r="E84" s="16">
-        <v>1</v>
-      </c>
-      <c r="F84" s="16">
+      <c r="E84" s="9">
+        <v>1</v>
+      </c>
+      <c r="F84" s="9">
         <v>2025</v>
       </c>
-      <c r="G84" s="16" t="s">
+      <c r="G84" s="9" t="s">
         <v>138</v>
       </c>
       <c r="H84" s="2">
@@ -2948,25 +3029,25 @@
       <c r="AB84" s="2"/>
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A85" s="16">
+      <c r="A85" s="9">
         <v>8</v>
       </c>
-      <c r="B85" s="16">
+      <c r="B85" s="9">
         <v>108</v>
       </c>
-      <c r="C85" s="16">
+      <c r="C85" s="9">
         <v>2</v>
       </c>
-      <c r="D85" s="16">
+      <c r="D85" s="9">
         <v>15</v>
       </c>
-      <c r="E85" s="16">
-        <v>1</v>
-      </c>
-      <c r="F85" s="16">
+      <c r="E85" s="9">
+        <v>1</v>
+      </c>
+      <c r="F85" s="9">
         <v>2025</v>
       </c>
-      <c r="G85" s="16" t="s">
+      <c r="G85" s="9" t="s">
         <v>138</v>
       </c>
       <c r="H85" s="2">
@@ -3010,25 +3091,25 @@
       <c r="AB85" s="2"/>
     </row>
     <row r="86" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A86" s="16">
+      <c r="A86" s="9">
         <v>9</v>
       </c>
-      <c r="B86" s="16">
+      <c r="B86" s="9">
         <v>109</v>
       </c>
-      <c r="C86" s="16">
+      <c r="C86" s="9">
         <v>3</v>
       </c>
-      <c r="D86" s="16">
+      <c r="D86" s="9">
         <v>15</v>
       </c>
-      <c r="E86" s="16">
-        <v>1</v>
-      </c>
-      <c r="F86" s="16">
+      <c r="E86" s="9">
+        <v>1</v>
+      </c>
+      <c r="F86" s="9">
         <v>2025</v>
       </c>
-      <c r="G86" s="16" t="s">
+      <c r="G86" s="9" t="s">
         <v>138</v>
       </c>
       <c r="H86" s="2">
@@ -3072,25 +3153,25 @@
       <c r="AB86" s="2"/>
     </row>
     <row r="87" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A87" s="16">
+      <c r="A87" s="9">
         <v>10</v>
       </c>
-      <c r="B87" s="16">
+      <c r="B87" s="9">
         <v>109</v>
       </c>
-      <c r="C87" s="16">
+      <c r="C87" s="9">
         <v>3</v>
       </c>
-      <c r="D87" s="16">
+      <c r="D87" s="9">
         <v>15</v>
       </c>
-      <c r="E87" s="16">
+      <c r="E87" s="9">
         <v>2</v>
       </c>
-      <c r="F87" s="16">
+      <c r="F87" s="9">
         <v>2025</v>
       </c>
-      <c r="G87" s="16" t="s">
+      <c r="G87" s="9" t="s">
         <v>139</v>
       </c>
       <c r="H87" s="2">
@@ -3399,4 +3480,1701 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F158A5-E275-42BB-A620-56DC5E56E09D}">
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" s="2">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="2">
+        <v>500</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" s="2">
+        <v>500</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="2">
+        <v>3</v>
+      </c>
+      <c r="E20" s="2">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>10</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="2">
+        <v>50</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D23" s="2">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2">
+        <v>27</v>
+      </c>
+      <c r="F23" s="2">
+        <v>7</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" s="2">
+        <v>50</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="2">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2">
+        <v>27</v>
+      </c>
+      <c r="F25" s="2">
+        <v>7</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" s="2">
+        <v>500</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE99C1B1-4639-4AD6-BFD7-70B194FAE9A2}">
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="2">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="2">
+        <v>150</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="2">
+        <v>150</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="2">
+        <v>150</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="2">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="2">
+        <v>150</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="2">
+        <v>200</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="2">
+        <v>150</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="2">
+        <v>20</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" s="2">
+        <v>150</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="2">
+        <v>50</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="2">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2">
+        <v>27</v>
+      </c>
+      <c r="F16" s="2">
+        <v>7</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="2">
+        <v>50</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" s="2">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2">
+        <v>27</v>
+      </c>
+      <c r="F18" s="2">
+        <v>7</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04992067-F4B3-46FB-B7C9-06976FF6218A}">
+  <dimension ref="A1:AB4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>115</v>
+      </c>
+      <c r="R1" t="s">
+        <v>116</v>
+      </c>
+      <c r="S1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T1" t="s">
+        <v>118</v>
+      </c>
+      <c r="U1" t="s">
+        <v>119</v>
+      </c>
+      <c r="V1" t="s">
+        <v>120</v>
+      </c>
+      <c r="W1" t="s">
+        <v>6</v>
+      </c>
+      <c r="X1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I4" t="s">
+        <v>154</v>
+      </c>
+      <c r="J4" t="s">
+        <v>155</v>
+      </c>
+      <c r="K4" t="s">
+        <v>156</v>
+      </c>
+      <c r="L4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M4" t="s">
+        <v>158</v>
+      </c>
+      <c r="N4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>